--- a/low_stock_medicines.xlsx
+++ b/low_stock_medicines.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,179 +463,179 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MOUNJARO 2.5 MG KWIKPEN</t>
+          <t>ACC-CHECK INSTANT FOR W GLUCOMETER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>D912974</t>
+          <t>91800097</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13125</v>
+        <v>1450</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2027-01-05</t>
+          <t>2028-02-01</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DISPOVAN 32G PEN NEEDLES</t>
+          <t>ACCU-CHECK INSTANT GLUCOSTRIP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>544N</t>
+          <t>303837</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>1115</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2030-01-09</t>
+          <t>2027-03-01</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EMPHA M 12.5/500</t>
+          <t>ACCU-CHECK INSTANT'SS COMBO( GLUCOMETER+ STRIP OF 10)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>N2500670</t>
+          <t>92200173</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>109</v>
+        <v>820</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2028-04-01</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ALSITA MP 500</t>
+          <t>BASUGINE 3ML CATRIDGE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25443008</t>
+          <t>122509141</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>203</v>
+        <v>651.95</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2028-08-01</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OLKEM 20</t>
+          <t>BASUGINE DESPOSABLE PEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25443043</t>
+          <t>122506012D</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>243</v>
+        <v>782.35</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2028-05-01</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OXRAMET S XR 10/100/500 1*7</t>
+          <t>BRO-ZEDEX SF COUGH SYP SF</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GTG3613A</t>
+          <t>D250602</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>149</v>
+        <v>187.68</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2027-12-31</t>
+          <t>2027-09-01</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AZTOR 20 MG TAB</t>
+          <t>CANDID B CREAM 20 GM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GTG1449B</t>
+          <t>11251184</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>214</v>
+        <v>178.12</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2028-01-04</t>
+          <t>2027-07-01</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -645,49 +645,49 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ROSUVAS 5 MG TAB</t>
+          <t>EVALON CREAM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SIG1784A</t>
+          <t>B01325C</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>210</v>
+        <v>524.05</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2028-01-01</t>
+          <t>2028-02-01</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SITARA M 100/500</t>
+          <t>EVION-LC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EMV252758C</t>
+          <t>2 batches</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>6.45</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2027-01-10</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -697,23 +697,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SITARED M  50/500 MG TAB</t>
+          <t>FERISOME-TAB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SIG2194A</t>
+          <t>FRSMGC020</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>177</v>
+        <v>20.64</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2027-05-01</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -723,257 +723,259 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SITARED M  50/500 MG TAB</t>
+          <t>FOLIGRAF 1200 IU8ML CART</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SIG2272B</t>
+          <t>2 batches</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>177</v>
+        <v>34687.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2027-01-10</t>
+          <t>2027-08-01</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SITARED M XR 100/1000 MG TAB (1*10)</t>
+          <t>GINETTE 35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GTF1664B</t>
+          <t>25S2HTA53</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>159</v>
+        <v>478.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2027-05-01</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GEMER 1 TAB</t>
+          <t>MONJARO 15 MG KWIK PEN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GTG3066A</t>
+          <t>D938367</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>167</v>
+        <v>25781</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2027-09-01</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GEMER 2 TAB</t>
+          <t>MONJARO 2.5 MG KWIK PEN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GTG3180A</t>
+          <t>D912974</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>237</v>
+        <v>13125</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2027-05-01</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>THYRONORM 12.5 MCG</t>
+          <t>MONJARO 5 MG KWIK PEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AEL0477</t>
+          <t>2 batches</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>190</v>
+        <v>16406.25</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-05-01</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>THYRONORM 25 MCG</t>
+          <t>NEOGADINE ELIXIR SYP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TMB25278</t>
+          <t>B02K25098</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>186</v>
+        <v>233.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>THYRONORM 37.5 MCG</t>
+          <t>NOVOFINE NEEDLE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TMC25063*</t>
+          <t>4 batches</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>188</v>
+        <v>4</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2028-03-01</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>THYRONORM 50 MCG</t>
+          <t>OZEMPIC 0.25 MG PEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TMD25396*</t>
+          <t>RP5V726</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>132</v>
+        <v>8800</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2027-01-10</t>
+          <t>2028-07-01</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>THYRONORM 62.5 MCG</t>
+          <t>PEN NEEDLE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EBRF5036*</t>
+          <t>5056002</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>220</v>
+        <v>20.25</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2030-02-01</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>THYRONORM 75 MCG</t>
+          <t>SITARA M 100\500</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TMF25182*</t>
+          <t>2 batches</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>184</v>
+        <v>16.383</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2027-10-01</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -983,49 +985,49 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>THYRONORM 88 MCG</t>
+          <t>SITARED M 50/500</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EBRG5028*</t>
+          <t>2 batches</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>211</v>
+        <v>11.75</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2027-09-01</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>THYRONORM 100 MCG</t>
+          <t>SYSCAN-150</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TMH25258</t>
+          <t>CBD2M001</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>169</v>
+        <v>20.17</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2027-11-01</t>
+          <t>2028-01-01</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1035,75 +1037,77 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>THYRONORM 112 MCG</t>
+          <t>T-BACT OINT 5GM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EBRH5005</t>
+          <t>K73K</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>213</v>
+        <v>108.36</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2027-11-30</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>THYRONORM 125 MCG</t>
+          <t>THYRONORM 100</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EBRI5008</t>
+          <t>3 batches</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>216</v>
+        <v>168.82</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2027-07-01</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SHELCAL 500 TAB</t>
+          <t>THYRONORM 112</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>8LV2M362</t>
+          <t>2 batches</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
-      <c r="D26" t="n">
-        <v>159</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2027-07-07</t>
+          <t>2027-06-01</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1113,101 +1117,101 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ONDERO DM 500 TAB</t>
+          <t>THYRONORM 12.5</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GT251469</t>
+          <t>2 batches</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>230</v>
+        <v>189.72</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2027-07-07</t>
+          <t>2027-07-01</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NUROKIND-LC</t>
+          <t>THYRONORM 125</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>b95y125</t>
+          <t>2 batches</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>238</v>
+        <v>216.63</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2027-08-01</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FOLIGRAF 1200 IU 8ML (2 ML MULTIDOSE PEN)</t>
+          <t>THYRONORM 25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B25125018</t>
+          <t>2 batches</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>34688</v>
+        <v>185.4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2027-08-08</t>
+          <t>2027-09-01</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MOUNJARO 15 MG KWIKPEN</t>
+          <t>THYRONORM 37.5</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>D938367</t>
+          <t>TMC25063*</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>25781</v>
+        <v>187.85</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2027-09-09</t>
+          <t>2027-08-01</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1217,23 +1221,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TRIGLYNASE 2 TAB</t>
+          <t>THYRONORM 50</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>28027385</t>
+          <t>2 batches</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>94</v>
+        <v>132.02</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2027-10-01</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1243,153 +1247,155 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NEOGADINE ELEXIR LIQ</t>
+          <t>THYRONORM 62.5</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BO2K25098</t>
+          <t>2 batches</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>234</v>
+        <v>206.37</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2027-01-03</t>
+          <t>2027-07-01</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MEPRATE TAB</t>
+          <t>THYRONORM 75</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CUE18AEA</t>
+          <t>3 batches</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>67</v>
+        <v>183.97</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2028-01-09</t>
+          <t>2027-08-01</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CIPLAR 10</t>
+          <t>THYRONORM 88</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5SB0676</t>
+          <t>2 batches</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
-      </c>
-      <c r="D34" t="n">
-        <v>23</v>
+        <v>2</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2028-01-07</t>
+          <t>2027-08-01</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STEMETIL MD (1*15)</t>
+          <t>TRIGLYNASE-2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SEA25022</t>
+          <t>2 batches</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>190</v>
+        <v>9.352</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2027-03-01</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CABGOLIN-0.25</t>
+          <t>XGLAR CART</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GTG2721A</t>
+          <t>C241GH4010</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>252</v>
+        <v>640.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-06-01</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CABGOLIN-0.5</t>
+          <t>XSULIN R VIAL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GTG1713A</t>
+          <t>A032515016</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>549</v>
+        <v>181.39</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2027-04-01</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1399,989 +1405,53 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>T BACT OINTMENT 5GM</t>
+          <t>YURPEAK 2.5MG/0.6ML PEN</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>K73K</t>
+          <t>D921081</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>115</v>
+        <v>13125</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2027-05-01</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GINETTE 35</t>
+          <t>ZEDEX-SF COUGH SYP</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>25S2HTA663</t>
+          <t>2 batches</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>478</v>
+        <v>190.31</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2027-09-01</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>VSL-3 CAP</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>JMG1096A</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>2</v>
-      </c>
-      <c r="D40" t="n">
-        <v>452</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2027-01-09</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>EVION-LC</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>5268C82301</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" t="n">
-        <v>65</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2027-01-02</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>TRYPTOMER-10</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>D2500387</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>4</v>
-      </c>
-      <c r="D42" t="n">
-        <v>77</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2027-01-10</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
         <v>6</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>NAXDOM-500</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>FHC0946</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>2</v>
-      </c>
-      <c r="D43" t="n">
-        <v>176</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2028-01-09</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>ONDEM MD 4</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>25442254</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>3</v>
-      </c>
-      <c r="D44" t="n">
-        <v>59</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2027-01-05</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>ZINCOVIT</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>ZVT25220</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" t="n">
-        <v>108</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2027-01-02</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>HUCOG 2000HP LIQ</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>B10725001</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" t="n">
-        <v>367</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2027-01-04</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>THYRONORM 75 MCG</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>TMF25209</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>2</v>
-      </c>
-      <c r="D47" t="n">
-        <v>184</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2027-01-10</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>THYRONORM 75 MCG</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>TMF25231</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" t="n">
-        <v>184</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2027-01-10</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>THYRONORM 88 MCG</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>EBRG5036</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>2</v>
-      </c>
-      <c r="D49" t="n">
-        <v>211</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2027-01-09</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>THYRONORM 25 MCG</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>TMB25292</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>2</v>
-      </c>
-      <c r="D50" t="n">
-        <v>186</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2027-01-10</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>THYRONORM 100 MCG</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>TMH25217</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" t="n">
-        <v>180</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2027-01-07</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>YURPEAK (TIRZEPATIDE) 2.5 MG KWIKPEN INJECTION 1*1</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>D921081</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" t="n">
-        <v>13125</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>2027-01-05</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>BD ULTRA FINE PEN NEEDLES 4mm 32 G</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>*****</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" t="n">
-        <v>100</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2027-01-05</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>MOUNJARO 5 MG KWIKPEN</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>D919450</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="n">
-        <v>16406</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>2027-01-05</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>DISPOVAN 32G PEN NEEDLES</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>317B</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="n">
-        <v>15</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>2028-01-03</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>SHELCAL 500 TAB</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>8LV2M349</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" t="n">
-        <v>159</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2027-01-06</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>NUROKIND LC</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>B95Y128</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" t="n">
-        <v>239</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2027-01-08</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>ZINCOVIT</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>ZVT25220</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" t="n">
-        <v>108</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>2027-01-02</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JUSLINA M 2.5/500 </t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>B60AY003</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>3</v>
-      </c>
-      <c r="D59" t="n">
-        <v>77</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2027-01-05</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GEMER 2 </t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>GTG3179A</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>2</v>
-      </c>
-      <c r="D60" t="n">
-        <v>237</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2027-01-09</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>TRIGLYNASE 2</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>28027306</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" t="n">
-        <v>94</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>2027-01-03</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>BRO-ZEDEX SF</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>D250602</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" t="n">
-        <v>188</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>2027-01-09</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>ZEDEX SF</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>D250570</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" t="n">
-        <v>190</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>2027-01-09</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>XGLAR REFILL</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>C24IGH4010</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>4</v>
-      </c>
-      <c r="D64" t="n">
-        <v>640</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>2027-06-30</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>BRO-ZEDEX SF</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>D250602</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>2</v>
-      </c>
-      <c r="D65" t="n">
-        <v>187</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>2027-03-09</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>XSULIN R VIAL</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>A032515016</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>5</v>
-      </c>
-      <c r="D66" t="n">
-        <v>181</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>2027-04-30</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>XSULIN R CART</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>TBB030225</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" t="n">
-        <v>375</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>2028-01-31</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>CANDID B CREAM 20G</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>11251184</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>2</v>
-      </c>
-      <c r="D68" t="n">
-        <v>178</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>2027-07-31</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>OVARAL L TAB</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>MR6546</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>3</v>
-      </c>
-      <c r="D69" t="n">
-        <v>68</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>EPLEHEF 25 MG</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>BRF09102A</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>4</v>
-      </c>
-      <c r="D70" t="n">
-        <v>246</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>2028-08-31</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>EPLEHEF 50 MG 1*10</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>BRF09103A</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>4</v>
-      </c>
-      <c r="D71" t="n">
-        <v>388</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>2028-09-30</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>EVALON CREAM 15 GM</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>B01325C</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>2</v>
-      </c>
-      <c r="D72" t="n">
-        <v>524</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>2028-02-28</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>SYSCAN-150 MG 1*1</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>CBD2M001</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>2</v>
-      </c>
-      <c r="D73" t="n">
-        <v>20</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>2028-01-31</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>BASUGINE 3ML CATRIDGE</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>122509141</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>2</v>
-      </c>
-      <c r="D74" t="n">
-        <v>651.95</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>2028-08-01</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>BASUGINE DESPOSABLE PEN 1PC</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>122506012D</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" t="n">
-        <v>782.35</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>08/28</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
